--- a/AMS/011-Cherry-Blossam/Cherry Blossom - FY_25-26_V2.xlsx
+++ b/AMS/011-Cherry-Blossam/Cherry Blossom - FY_25-26_V2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\011-Cherry-Blossam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB79C4D0-144E-4EB6-8064-9FE7C1283752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05907772-FEDB-4CCB-83DF-36CD8385543A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="1" r:id="rId1"/>
@@ -2021,7 +2021,7 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="292">
+  <cellXfs count="291">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2560,37 +2560,44 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="49" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="45" fillId="0" borderId="35" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2606,38 +2613,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="49" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="45" fillId="0" borderId="35" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2715,9 +2715,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2955,16 +2952,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="23.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="250" t="s">
+      <c r="A1" s="240" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="252"/>
+      <c r="B1" s="229"/>
+      <c r="C1" s="229"/>
+      <c r="D1" s="229"/>
+      <c r="E1" s="229"/>
+      <c r="F1" s="229"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="230"/>
       <c r="I1" s="81"/>
       <c r="J1" s="81" t="str">
         <f>UPPER(A1)</f>
@@ -2988,16 +2985,16 @@
       <c r="Z1" s="81"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A2" s="235" t="s">
+      <c r="A2" s="241" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243"/>
       <c r="I2" s="81"/>
       <c r="J2" s="81" t="s">
         <v>241</v>
@@ -3020,16 +3017,16 @@
       <c r="Z2" s="81"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A3" s="235" t="s">
+      <c r="A3" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="236"/>
-      <c r="C3" s="236"/>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
-      <c r="F3" s="236"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243"/>
       <c r="I3" s="81"/>
       <c r="J3" s="81"/>
       <c r="K3" s="81"/>
@@ -3050,16 +3047,16 @@
       <c r="Z3" s="81"/>
     </row>
     <row r="4" spans="1:26" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="253" t="s">
+      <c r="A4" s="244" t="s">
         <v>234</v>
       </c>
-      <c r="B4" s="236"/>
-      <c r="C4" s="236"/>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="237"/>
+      <c r="B4" s="242"/>
+      <c r="C4" s="242"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="243"/>
       <c r="I4" s="81"/>
       <c r="J4" s="81"/>
       <c r="K4" s="81"/>
@@ -3113,10 +3110,10 @@
       <c r="A6" s="157" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="254" t="s">
+      <c r="B6" s="245" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="231"/>
+      <c r="C6" s="239"/>
       <c r="D6" s="203" t="s">
         <v>191</v>
       </c>
@@ -3124,10 +3121,10 @@
         <f>A6</f>
         <v>FY 2024-25</v>
       </c>
-      <c r="F6" s="254" t="s">
+      <c r="F6" s="245" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="231"/>
+      <c r="G6" s="239"/>
       <c r="H6" s="158" t="str">
         <f>D6</f>
         <v>FY 2025-26</v>
@@ -3260,10 +3257,10 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" s="165"/>
-      <c r="B10" s="255" t="s">
+      <c r="B10" s="234" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="256"/>
+      <c r="C10" s="235"/>
       <c r="D10" s="206"/>
       <c r="E10" s="166">
         <v>11113.85</v>
@@ -3405,10 +3402,10 @@
     </row>
     <row r="14" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="164"/>
-      <c r="B14" s="248" t="s">
+      <c r="B14" s="236" t="s">
         <v>247</v>
       </c>
-      <c r="C14" s="249"/>
+      <c r="C14" s="253"/>
       <c r="D14" s="209"/>
       <c r="E14" s="169">
         <v>2128540</v>
@@ -3767,10 +3764,10 @@
       <c r="E23" s="169">
         <v>100000</v>
       </c>
-      <c r="F23" s="248" t="s">
+      <c r="F23" s="236" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="256"/>
+      <c r="G23" s="235"/>
       <c r="H23" s="101">
         <f>'Sch-III,IV,V'!C8</f>
         <v>100000</v>
@@ -3838,10 +3835,10 @@
       <c r="E25" s="169">
         <v>15586</v>
       </c>
-      <c r="F25" s="257" t="s">
+      <c r="F25" s="237" t="s">
         <v>30</v>
       </c>
-      <c r="G25" s="256"/>
+      <c r="G25" s="235"/>
       <c r="H25" s="101">
         <v>29052</v>
       </c>
@@ -3916,10 +3913,10 @@
       <c r="E27" s="169">
         <v>3044199</v>
       </c>
-      <c r="F27" s="257" t="s">
+      <c r="F27" s="237" t="s">
         <v>32</v>
       </c>
-      <c r="G27" s="256"/>
+      <c r="G27" s="235"/>
       <c r="H27" s="173">
         <f>'FA-Sch II'!H9</f>
         <v>3037031</v>
@@ -4467,10 +4464,10 @@
         <f>SUM(A11:A42)</f>
         <v>5623763</v>
       </c>
-      <c r="B43" s="230" t="s">
+      <c r="B43" s="238" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="231"/>
+      <c r="C43" s="239"/>
       <c r="D43" s="211">
         <f>SUM(D11:D42)</f>
         <v>5869496</v>
@@ -4479,10 +4476,10 @@
         <f>SUM(E7:E42)</f>
         <v>5623763</v>
       </c>
-      <c r="F43" s="230" t="s">
+      <c r="F43" s="238" t="s">
         <v>44</v>
       </c>
-      <c r="G43" s="231"/>
+      <c r="G43" s="239"/>
       <c r="H43" s="177">
         <f>SUM(H7:H42)</f>
         <v>5869496</v>
@@ -4511,9 +4508,9 @@
       <c r="B44" s="178"/>
       <c r="C44" s="137"/>
       <c r="D44" s="138"/>
-      <c r="E44" s="243"/>
-      <c r="F44" s="243"/>
-      <c r="G44" s="243"/>
+      <c r="E44" s="246"/>
+      <c r="F44" s="246"/>
+      <c r="G44" s="246"/>
       <c r="H44" s="139"/>
       <c r="I44" s="81"/>
       <c r="J44" s="81"/>
@@ -4565,11 +4562,11 @@
       <c r="A46" s="144"/>
       <c r="D46" s="145"/>
       <c r="E46" s="146"/>
-      <c r="F46" s="244" t="s">
+      <c r="F46" s="247" t="s">
         <v>246</v>
       </c>
-      <c r="G46" s="244"/>
-      <c r="H46" s="245"/>
+      <c r="G46" s="247"/>
+      <c r="H46" s="248"/>
       <c r="I46" s="81"/>
       <c r="J46" s="81"/>
       <c r="K46" s="81"/>
@@ -4697,18 +4694,18 @@
       <c r="C51" s="181"/>
       <c r="D51" s="145"/>
       <c r="E51" s="146"/>
-      <c r="F51" s="246" t="s">
+      <c r="F51" s="249" t="s">
         <v>245</v>
       </c>
-      <c r="G51" s="246"/>
-      <c r="H51" s="247"/>
+      <c r="G51" s="249"/>
+      <c r="H51" s="250"/>
     </row>
     <row r="52" spans="1:26" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="228">
-        <v>46250</v>
-      </c>
-      <c r="B52" s="229"/>
-      <c r="C52" s="229"/>
+      <c r="A52" s="251">
+        <v>46276</v>
+      </c>
+      <c r="B52" s="252"/>
+      <c r="C52" s="252"/>
       <c r="D52" s="150"/>
       <c r="E52" s="151"/>
       <c r="F52" s="152"/>
@@ -4756,27 +4753,27 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="F6:G6"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="F43:G43"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.39370078740157483" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4798,52 +4795,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="232" t="s">
+      <c r="A1" s="254" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="233"/>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="234"/>
+      <c r="B1" s="255"/>
+      <c r="C1" s="255"/>
+      <c r="D1" s="255"/>
+      <c r="E1" s="255"/>
+      <c r="F1" s="255"/>
+      <c r="G1" s="255"/>
+      <c r="H1" s="256"/>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="235" t="s">
+      <c r="A2" s="241" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="236"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237"/>
+      <c r="B2" s="242"/>
+      <c r="C2" s="242"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="242"/>
+      <c r="H2" s="243"/>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="235" t="s">
+      <c r="A3" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="236"/>
-      <c r="C3" s="236"/>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
-      <c r="F3" s="236"/>
-      <c r="G3" s="236"/>
-      <c r="H3" s="237"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="242"/>
+      <c r="H3" s="243"/>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="238" t="s">
+      <c r="A4" s="257" t="s">
         <v>206</v>
       </c>
-      <c r="B4" s="236"/>
-      <c r="C4" s="236"/>
-      <c r="D4" s="236"/>
-      <c r="E4" s="236"/>
-      <c r="F4" s="236"/>
-      <c r="G4" s="236"/>
-      <c r="H4" s="237"/>
+      <c r="B4" s="242"/>
+      <c r="C4" s="242"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="243"/>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="182"/>
@@ -4861,10 +4858,10 @@
       <c r="A6" s="215" t="s">
         <v>145</v>
       </c>
-      <c r="B6" s="239" t="s">
+      <c r="B6" s="258" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="240"/>
+      <c r="C6" s="259"/>
       <c r="D6" s="216" t="s">
         <v>205</v>
       </c>
@@ -4872,10 +4869,10 @@
         <f>A6</f>
         <v>FY 24-25</v>
       </c>
-      <c r="F6" s="241" t="s">
+      <c r="F6" s="260" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="242"/>
+      <c r="G6" s="261"/>
       <c r="H6" s="185" t="str">
         <f>D6</f>
         <v>FY 25-26</v>
@@ -5463,10 +5460,10 @@
         <f>SUM(A7:A31)</f>
         <v>930859.8</v>
       </c>
-      <c r="B35" s="230" t="s">
+      <c r="B35" s="238" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="231"/>
+      <c r="C35" s="239"/>
       <c r="D35" s="223">
         <f>SUM(D7:D34)</f>
         <v>621721.80000000005</v>
@@ -5475,10 +5472,10 @@
         <f>SUM(E7:E34)</f>
         <v>930859.8</v>
       </c>
-      <c r="F35" s="230" t="s">
+      <c r="F35" s="238" t="s">
         <v>44</v>
       </c>
-      <c r="G35" s="231"/>
+      <c r="G35" s="239"/>
       <c r="H35" s="201">
         <f>SUM(H7:H34)</f>
         <v>621721.80000000005</v>
@@ -5489,9 +5486,9 @@
       <c r="B36" s="178"/>
       <c r="C36" s="137"/>
       <c r="D36" s="138"/>
-      <c r="E36" s="243"/>
-      <c r="F36" s="243"/>
-      <c r="G36" s="243"/>
+      <c r="E36" s="246"/>
+      <c r="F36" s="246"/>
+      <c r="G36" s="246"/>
       <c r="H36" s="139"/>
     </row>
     <row r="37" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5515,11 +5512,11 @@
       <c r="A38" s="144"/>
       <c r="D38" s="145"/>
       <c r="E38" s="146"/>
-      <c r="F38" s="244" t="s">
+      <c r="F38" s="247" t="s">
         <v>246</v>
       </c>
-      <c r="G38" s="244"/>
-      <c r="H38" s="245"/>
+      <c r="G38" s="247"/>
+      <c r="H38" s="248"/>
     </row>
     <row r="39" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="144"/>
@@ -5571,18 +5568,18 @@
       <c r="C43" s="181"/>
       <c r="D43" s="145"/>
       <c r="E43" s="146"/>
-      <c r="F43" s="246" t="s">
+      <c r="F43" s="249" t="s">
         <v>245</v>
       </c>
-      <c r="G43" s="246"/>
-      <c r="H43" s="247"/>
+      <c r="G43" s="249"/>
+      <c r="H43" s="250"/>
     </row>
     <row r="44" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="228">
-        <v>46250</v>
-      </c>
-      <c r="B44" s="229"/>
-      <c r="C44" s="229"/>
+      <c r="A44" s="251">
+        <v>46276</v>
+      </c>
+      <c r="B44" s="252"/>
+      <c r="C44" s="252"/>
       <c r="D44" s="150"/>
       <c r="E44" s="151"/>
       <c r="F44" s="152"/>
@@ -6575,7 +6572,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.59055118110236227" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6591,34 +6588,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="228" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="252"/>
+      <c r="B1" s="229"/>
+      <c r="C1" s="229"/>
+      <c r="D1" s="229"/>
+      <c r="E1" s="229"/>
+      <c r="F1" s="229"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="230"/>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="259" t="s">
+      <c r="A2" s="231" t="s">
         <v>235</v>
       </c>
-      <c r="B2" s="260"/>
-      <c r="C2" s="260"/>
-      <c r="D2" s="260"/>
-      <c r="E2" s="260"/>
-      <c r="F2" s="260"/>
-      <c r="G2" s="260"/>
-      <c r="H2" s="260"/>
-      <c r="I2" s="260"/>
-      <c r="J2" s="260"/>
-      <c r="K2" s="261"/>
+      <c r="B2" s="232"/>
+      <c r="C2" s="232"/>
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="232"/>
+      <c r="H2" s="232"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="233"/>
     </row>
     <row r="3" spans="1:11" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="112" t="s">
@@ -7651,7 +7648,7 @@
         <f t="shared" si="2"/>
         <v>137007</v>
       </c>
-      <c r="H32" s="291" t="s">
+      <c r="H32" s="56" t="s">
         <v>181</v>
       </c>
       <c r="I32" s="57">
@@ -15249,7 +15246,7 @@
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
     </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>117</v>
       </c>
@@ -15260,7 +15257,7 @@
       <c r="I4" s="283"/>
       <c r="J4" s="283"/>
     </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="271" t="s">
         <v>118</v>
       </c>
@@ -15274,7 +15271,7 @@
       <c r="J5" s="276"/>
       <c r="K5" s="277"/>
     </row>
-    <row r="6" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="128" t="s">
         <v>119</v>
       </c>
@@ -15300,7 +15297,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="107">
         <v>1</v>
       </c>
@@ -15326,11 +15323,11 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="274" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="242"/>
+      <c r="B8" s="261"/>
       <c r="C8" s="66">
         <f>SUM(C7:C7)</f>
         <v>100000</v>
@@ -15351,7 +15348,7 @@
         <v>4134</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="19.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="25"/>
       <c r="C9" s="73"/>
@@ -15371,7 +15368,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="25"/>
       <c r="C10" s="73"/>
@@ -15391,7 +15388,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>125</v>
       </c>
@@ -15412,7 +15409,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="284" t="s">
         <v>126</v>
       </c>
@@ -15434,7 +15431,7 @@
         <v>6637</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="127" t="s">
         <v>119</v>
       </c>
@@ -15460,7 +15457,7 @@
         <v>8417</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="124">
         <v>1</v>
       </c>
@@ -15487,7 +15484,7 @@
         <v>8500</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="32">
         <v>2</v>
       </c>
@@ -15513,7 +15510,7 @@
         <v>7548</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="32">
         <v>3</v>
       </c>
@@ -15539,7 +15536,7 @@
         <v>13652</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="32">
         <v>4</v>
       </c>
@@ -15560,7 +15557,7 @@
         <v>54467</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="19.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A18" s="32">
         <v>5</v>
       </c>
@@ -15571,7 +15568,7 @@
         <v>3410</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="32">
         <v>6</v>
       </c>
@@ -15582,7 +15579,7 @@
         <v>8105</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="32">
         <v>7</v>
       </c>
@@ -15593,7 +15590,7 @@
         <v>12980</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="32">
         <v>8</v>
       </c>
@@ -15604,11 +15601,11 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="270" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="242"/>
+      <c r="B22" s="261"/>
       <c r="C22" s="31">
         <f>SUM(C14:C21)</f>
         <v>38418</v>
@@ -18958,9 +18955,9 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="289"/>
-      <c r="B1" s="236"/>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="23"/>
@@ -20297,7 +20294,7 @@
       <c r="C1" s="290" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="236"/>
+      <c r="D1" s="242"/>
       <c r="E1" s="6" t="s">
         <v>140</v>
       </c>
